--- a/cds/mm_us-5year-cds.xlsx
+++ b/cds/mm_us-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="946">
   <si>
     <t>Date</t>
   </si>
@@ -2838,6 +2838,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -3187,7 +3202,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B940"/>
+  <dimension ref="A1:B945"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -10708,6 +10723,46 @@
       </c>
       <c r="B940" s="3">
         <v>37.7594</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2">
+      <c r="A941" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B941" s="3">
+        <v>41.5865</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2">
+      <c r="A942" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B942" s="3">
+        <v>42.2611</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2">
+      <c r="A943" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B943" s="3">
+        <v>43.8074</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2">
+      <c r="A944" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B944" s="3">
+        <v>41.7842</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2">
+      <c r="A945" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="B945" s="3">
+        <v>39.3756</v>
       </c>
     </row>
   </sheetData>
